--- a/data/台股五維總篩選.xlsx
+++ b/data/台股五維總篩選.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -576,44 +576,44 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>264.7</v>
+        <v>421.7</v>
       </c>
       <c r="K2" t="n">
-        <v>85</v>
+        <v>41.1</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
       </c>
       <c r="N2" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="O2" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>15.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>61.9</v>
+        <v>90.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="S2" t="n">
-        <v>300.8</v>
+        <v>133.5</v>
       </c>
       <c r="T2" t="n">
-        <v>12.72</v>
+        <v>6.76</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -656,44 +656,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>11/12</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="J3" t="n">
-        <v>421.7</v>
+        <v>264.7</v>
       </c>
       <c r="K3" t="n">
-        <v>41.1</v>
+        <v>85</v>
       </c>
       <c r="L3" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>17.9</v>
+        <v>15.5</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="P3" t="n">
-        <v>24.5</v>
+        <v>15.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>90.5</v>
+        <v>61.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>133.5</v>
+        <v>300.8</v>
       </c>
       <c r="T3" t="n">
-        <v>6.76</v>
+        <v>12.72</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -878,12 +878,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>✔✔··✔  (成長現金估值品質資金)</t>
+          <t>✔··✔✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>估值／品質</t>
+          <t>現金／估值</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -896,60 +896,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>11/12</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.71</v>
+        <v>3.26</v>
       </c>
       <c r="J6" t="n">
-        <v>44.6</v>
+        <v>-148</v>
       </c>
       <c r="K6" t="n">
-        <v>107.5</v>
+        <v>56.9</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>12.8</v>
       </c>
       <c r="O6" t="n">
-        <v>28.6</v>
+        <v>57.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.8</v>
+        <v>57.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.45</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>320.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS創52週高／RS上升／週斜率為正／週斜率加速／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -962,12 +958,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>✔··✔✔  (成長現金估值品質資金)</t>
+          <t>✔✔··✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>現金／估值</t>
+          <t>估值／品質</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -980,49 +976,53 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.26</v>
+        <v>1.71</v>
       </c>
       <c r="J7" t="n">
-        <v>-148</v>
+        <v>44.6</v>
       </c>
       <c r="K7" t="n">
-        <v>56.9</v>
+        <v>107.5</v>
       </c>
       <c r="L7" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>12.8</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>57.1</v>
+        <v>28.6</v>
       </c>
       <c r="P7" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.1</v>
+        <v>23.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="S7" t="n">
-        <v>94.40000000000001</v>
+        <v>320.4</v>
       </c>
       <c r="T7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>13.73</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS創52週高／RS上升／週斜率為正／週斜率加速／大盤多頭</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1109,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>○ 偏多</t>
+          <t>🔥 燒錢成長(成長吞現金)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>✔✔··✔  (成長現金估值品質資金)</t>
+          <t>✔··✔✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>估值／品質</t>
+          <t>現金／估值</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1136,74 +1136,78 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.26</v>
+        <v>-3.39</v>
       </c>
       <c r="J9" t="n">
-        <v>821.7</v>
+        <v>-2638.2</v>
       </c>
       <c r="K9" t="n">
-        <v>18.5</v>
+        <v>16.2</v>
       </c>
       <c r="L9" t="n">
-        <v>68.90000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="M9" t="n">
-        <v>87.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="N9" t="n">
-        <v>9.1</v>
+        <v>23.5</v>
       </c>
       <c r="O9" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="P9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>81</v>
+      </c>
       <c r="R9" t="n">
-        <v>3.85</v>
+        <v>3.41</v>
       </c>
       <c r="S9" t="n">
-        <v>-60.7</v>
+        <v>-61</v>
       </c>
       <c r="T9" t="n">
-        <v>0.92</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🏔 估值透支(好公司但太貴)</t>
+          <t>🔥 燒錢成長(成長吞現金)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>✔✔··✔  (成長現金估值品質資金)</t>
+          <t>✔··✔✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>估值／品質</t>
+          <t>現金／估值</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1212,56 +1216,60 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.92</v>
+        <v>-0.64</v>
       </c>
       <c r="J10" t="n">
-        <v>784.3</v>
+        <v>-315.6</v>
       </c>
       <c r="K10" t="n">
-        <v>17.3</v>
+        <v>14.1</v>
       </c>
       <c r="L10" t="n">
-        <v>97</v>
+        <v>59.9</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N10" t="n">
         <v>14.4</v>
       </c>
       <c r="O10" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+        <v>61.9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>52.4</v>
+      </c>
       <c r="R10" t="n">
-        <v>3.48</v>
+        <v>5.32</v>
       </c>
       <c r="S10" t="n">
-        <v>-10.9</v>
+        <v>-43.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.39</v>
+        <v>3.57</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1292,44 +1300,44 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>11/12</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.64</v>
+        <v>-1.14</v>
       </c>
       <c r="J11" t="n">
-        <v>-315.6</v>
+        <v>-189.1</v>
       </c>
       <c r="K11" t="n">
-        <v>14.1</v>
+        <v>16.1</v>
       </c>
       <c r="L11" t="n">
-        <v>59.9</v>
+        <v>47.1</v>
       </c>
       <c r="M11" t="n">
-        <v>97.5</v>
+        <v>75.8</v>
       </c>
       <c r="N11" t="n">
-        <v>14.4</v>
+        <v>23.2</v>
       </c>
       <c r="O11" t="n">
-        <v>61.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>11.9</v>
+        <v>112.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="R11" t="n">
-        <v>5.32</v>
+        <v>3.49</v>
       </c>
       <c r="S11" t="n">
-        <v>-43.9</v>
+        <v>-31.8</v>
       </c>
       <c r="T11" t="n">
-        <v>3.57</v>
+        <v>3.83</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
@@ -1341,247 +1349,251 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>⚠ 純資金(投機/慎防假突破)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>✔··✔✔  (成長現金估值品質資金)</t>
+          <t>·✔··✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>現金／估值</t>
+          <t>成長／估值／品質</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>7/12</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-1.14</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>-189.1</v>
+        <v>184.5</v>
       </c>
       <c r="K12" t="n">
-        <v>16.1</v>
+        <v>29.5</v>
       </c>
       <c r="L12" t="n">
-        <v>47.1</v>
+        <v>94.8</v>
       </c>
       <c r="M12" t="n">
-        <v>75.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>23.2</v>
+        <v>31.7</v>
       </c>
       <c r="O12" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="P12" t="n">
-        <v>112.1</v>
+        <v>31.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="R12" t="n">
-        <v>3.49</v>
+        <v>3.05</v>
       </c>
       <c r="S12" t="n">
-        <v>-31.8</v>
+        <v>-22.8</v>
       </c>
       <c r="T12" t="n">
-        <v>3.83</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>○ 偏多</t>
+          <t>⚠ 純資金(投機/慎防假突破)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>✔✔··✔  (成長現金估值品質資金)</t>
+          <t>·✔··✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>估值／品質</t>
+          <t>成長／估值／品質</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>9/12</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.78</v>
+        <v>1.96</v>
       </c>
       <c r="J13" t="n">
-        <v>798.1</v>
+        <v>519</v>
       </c>
       <c r="K13" t="n">
-        <v>18.5</v>
+        <v>36.6</v>
       </c>
       <c r="L13" t="n">
-        <v>82.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+        <v>47.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R13" t="n">
-        <v>3.78</v>
+        <v>1.79</v>
       </c>
       <c r="S13" t="n">
-        <v>-46.9</v>
+        <v>134.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0.29</v>
+        <v>8.99</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>⚠ 純資金(投機/慎防假突破)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>✔··✔✔  (成長現金估值品質資金)</t>
+          <t>✔···✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>現金／估值</t>
+          <t>現金／估值／品質</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-3.39</v>
+        <v>0.23</v>
       </c>
       <c r="J14" t="n">
-        <v>-2638.2</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>16.2</v>
+        <v>146.2</v>
       </c>
       <c r="L14" t="n">
-        <v>62.4</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>81.7</v>
+        <v>99.2</v>
       </c>
       <c r="N14" t="n">
-        <v>23.5</v>
+        <v>30.5</v>
       </c>
       <c r="O14" t="n">
-        <v>100</v>
+        <v>61.9</v>
       </c>
       <c r="P14" t="n">
-        <v>24.9</v>
+        <v>57.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>81</v>
+        <v>28.6</v>
       </c>
       <c r="R14" t="n">
-        <v>3.41</v>
+        <v>0.41</v>
       </c>
       <c r="S14" t="n">
-        <v>-61</v>
+        <v>50.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>6.03</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1604,60 +1616,64 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>8/12</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1773.9</v>
+        <v>1155.6</v>
       </c>
       <c r="K15" t="n">
-        <v>17.5</v>
+        <v>70</v>
       </c>
       <c r="L15" t="n">
-        <v>90</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>13.1</v>
+        <v>25.3</v>
       </c>
       <c r="O15" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>52.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>42.9</v>
+      </c>
       <c r="R15" t="n">
-        <v>3.03</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5</v>
+        <v>136.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.53</v>
+        <v>10.4</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1666,12 +1682,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>·✔··✔  (成長現金估值品質資金)</t>
+          <t>···✔✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>成長／估值／品質</t>
+          <t>成長／現金／估值</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1680,64 +1696,64 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>7/12</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.96</v>
+        <v>1.09</v>
       </c>
       <c r="J16" t="n">
-        <v>519</v>
+        <v>-1.8</v>
       </c>
       <c r="K16" t="n">
-        <v>36.6</v>
+        <v>25.7</v>
       </c>
       <c r="L16" t="n">
-        <v>92.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="M16" t="n">
-        <v>99.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="N16" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="O16" t="n">
-        <v>47.6</v>
+        <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>9.699999999999999</v>
+        <v>20.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.6</v>
+        <v>76.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.79</v>
+        <v>2.95</v>
       </c>
       <c r="S16" t="n">
-        <v>134.4</v>
+        <v>-20.6</v>
       </c>
       <c r="T16" t="n">
-        <v>8.99</v>
+        <v>5.03</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1746,12 +1762,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>·✔··✔  (成長現金估值品質資金)</t>
+          <t>··✔·✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>成長／估值／品質</t>
+          <t>成長／現金／品質</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1760,7 +1776,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1768,70 +1784,70 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.65</v>
       </c>
       <c r="J17" t="n">
-        <v>184.5</v>
+        <v>13.9</v>
       </c>
       <c r="K17" t="n">
-        <v>29.5</v>
+        <v>14.5</v>
       </c>
       <c r="L17" t="n">
-        <v>94.8</v>
+        <v>40.9</v>
       </c>
       <c r="M17" t="n">
-        <v>98.90000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="N17" t="n">
-        <v>31.7</v>
+        <v>14.7</v>
       </c>
       <c r="O17" t="n">
-        <v>57.1</v>
+        <v>38.1</v>
       </c>
       <c r="P17" t="n">
-        <v>31.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="S17" t="n">
-        <v>-22.8</v>
+        <v>-38.1</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>4.56</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>⚠ 純資金(投機/慎防假突破)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>·✔··✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／估值／品質</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1840,74 +1856,78 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-0.86</v>
+        <v>1.01</v>
       </c>
       <c r="J18" t="n">
-        <v>-403.8</v>
+        <v>135.6</v>
       </c>
       <c r="K18" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>51.9</v>
       </c>
       <c r="N18" t="n">
-        <v>12.1</v>
+        <v>20.6</v>
       </c>
       <c r="O18" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.8</v>
+      </c>
       <c r="R18" t="n">
-        <v>3.24</v>
+        <v>4.46</v>
       </c>
       <c r="S18" t="n">
-        <v>12.1</v>
+        <v>-44.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.36</v>
+        <v>2.48</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
+          <t>🔥 燒錢成長(成長吞現金)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>·✔··✔  (成長現金估值品質資金)</t>
+          <t>✔···✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>成長／估值／品質</t>
+          <t>現金／估值／品質</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1916,230 +1936,242 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>-0.87</v>
       </c>
       <c r="J19" t="n">
-        <v>1155.6</v>
+        <v>-840.7</v>
       </c>
       <c r="K19" t="n">
-        <v>70</v>
+        <v>18.9</v>
       </c>
       <c r="L19" t="n">
-        <v>99.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="M19" t="n">
-        <v>99.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="N19" t="n">
-        <v>25.3</v>
+        <v>35.3</v>
       </c>
       <c r="O19" t="n">
-        <v>52.4</v>
+        <v>95.2</v>
       </c>
       <c r="P19" t="n">
-        <v>33.9</v>
+        <v>52.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>42.9</v>
+        <v>38.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>4.15</v>
       </c>
       <c r="S19" t="n">
-        <v>136.3</v>
+        <v>-43.6</v>
       </c>
       <c r="T19" t="n">
-        <v>10.4</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>○ 偏多</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>✔✔···  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>估值／品質／資金</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-2.92</v>
+        <v>1.81</v>
       </c>
       <c r="J20" t="n">
-        <v>-550.4</v>
+        <v>378.2</v>
       </c>
       <c r="K20" t="n">
-        <v>14.3</v>
+        <v>39.4</v>
       </c>
       <c r="L20" t="n">
-        <v>23.5</v>
+        <v>88.3</v>
       </c>
       <c r="M20" t="n">
-        <v>86.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>8.300000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="O20" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-554.8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.8</v>
+      </c>
       <c r="R20" t="n">
-        <v>4.6</v>
+        <v>0.88</v>
       </c>
       <c r="S20" t="n">
-        <v>-62.2</v>
+        <v>8.6</v>
       </c>
       <c r="T20" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／均線多頭／週斜率為正／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>⚠ 純資金(投機/慎防假突破)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>····✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／現金／估值／品質</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>4/12</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.6899999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>-372.2</v>
+        <v>-130.1</v>
       </c>
       <c r="K21" t="n">
-        <v>15.9</v>
+        <v>68.5</v>
       </c>
       <c r="L21" t="n">
-        <v>82.3</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>99.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9.5</v>
+      </c>
       <c r="R21" t="n">
-        <v>3.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3</v>
+        <v>119.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>7.64</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS創52週高／RS上升／週斜率為正／週斜率加速／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>— 不符</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>···✔·  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／現金／估值／資金</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2148,74 +2180,78 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>7/12</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>-1.62</v>
+        <v>0.72</v>
       </c>
       <c r="J22" t="n">
-        <v>-453.5</v>
+        <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>16.7</v>
+        <v>40.4</v>
       </c>
       <c r="L22" t="n">
-        <v>75.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>89.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="N22" t="n">
         <v>9.4</v>
       </c>
       <c r="O22" t="n">
-        <v>81</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>61.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>61.9</v>
+      </c>
       <c r="R22" t="n">
-        <v>3.99</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>-56.2</v>
+        <v>94.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0.64</v>
+        <v>3.72</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
+          <t>🐢 穩定收租(牛皮績優·股息)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>·✔···  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／估值／品質／資金</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2224,78 +2260,78 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>3/12</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.23</v>
+        <v>2.28</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>172.6</v>
       </c>
       <c r="K23" t="n">
-        <v>146.2</v>
+        <v>19.1</v>
       </c>
       <c r="L23" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>99.2</v>
+        <v>45.2</v>
       </c>
       <c r="N23" t="n">
-        <v>30.5</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
-        <v>61.9</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>57.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0.41</v>
+        <v>4.84</v>
       </c>
       <c r="S23" t="n">
-        <v>50.1</v>
+        <v>-58.4</v>
       </c>
       <c r="T23" t="n">
-        <v>6.03</v>
+        <v>0.99</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
+          <t>🔥 燒錢成長(成長吞現金)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>··✔·✔  (成長現金估值品質資金)</t>
+          <t>✔····  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>成長／現金／品質</t>
+          <t>現金／估值／品質／資金</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2304,64 +2340,64 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="J24" t="n">
-        <v>13.9</v>
+        <v>-47.9</v>
       </c>
       <c r="K24" t="n">
-        <v>14.5</v>
+        <v>17.2</v>
       </c>
       <c r="L24" t="n">
-        <v>40.9</v>
+        <v>42.1</v>
       </c>
       <c r="M24" t="n">
-        <v>15.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>14.7</v>
+        <v>39.6</v>
       </c>
       <c r="O24" t="n">
-        <v>38.1</v>
+        <v>90.5</v>
       </c>
       <c r="P24" t="n">
-        <v>20.8</v>
+        <v>51.9</v>
       </c>
       <c r="Q24" t="n">
         <v>33.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="S24" t="n">
-        <v>-38.1</v>
+        <v>-59.4</v>
       </c>
       <c r="T24" t="n">
-        <v>4.56</v>
+        <v>4.14</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2370,78 +2406,74 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>···✔✔  (成長現金估值品質資金)</t>
+          <t>····✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>成長／現金／估值</t>
+          <t>成長／現金／估值／品質</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7/12</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.09</v>
-      </c>
+          <t>6/12</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>-1.8</v>
+        <v>-4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="L25" t="n">
-        <v>81.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>94.2</v>
+        <v>85</v>
       </c>
       <c r="N25" t="n">
-        <v>13.6</v>
+        <v>-2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="P25" t="n">
-        <v>20.7</v>
+        <v>-3</v>
       </c>
       <c r="Q25" t="n">
-        <v>76.2</v>
+        <v>23.8</v>
       </c>
       <c r="R25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-20.6</v>
+        <v>-47.8</v>
       </c>
       <c r="T25" t="n">
-        <v>5.03</v>
+        <v>1.35</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2450,17 +2482,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>·✔··✔  (成長現金估值品質資金)</t>
+          <t>····✔  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>成長／估值／品質</t>
+          <t>成長／現金／估值／品質</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2468,306 +2500,308 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>9/12</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.01</v>
+        <v>0.36</v>
       </c>
       <c r="J26" t="n">
-        <v>135.6</v>
+        <v>-8.4</v>
       </c>
       <c r="K26" t="n">
-        <v>21.2</v>
+        <v>84.5</v>
       </c>
       <c r="L26" t="n">
-        <v>95</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>51.9</v>
+        <v>62.1</v>
       </c>
       <c r="N26" t="n">
-        <v>20.6</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8</v>
+        <v>28.6</v>
       </c>
       <c r="P26" t="n">
-        <v>42</v>
+        <v>6.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>14.3</v>
       </c>
       <c r="R26" t="n">
-        <v>4.46</v>
+        <v>0.41</v>
       </c>
       <c r="S26" t="n">
-        <v>-44.3</v>
+        <v>140.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>7.01</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>— 不符</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>·····  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／現金／估值／品質／資金</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>0/12</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>-0.32</v>
+        <v>0.26</v>
       </c>
       <c r="J27" t="n">
-        <v>-98.5</v>
+        <v>1.6</v>
       </c>
       <c r="K27" t="n">
-        <v>19</v>
+        <v>64.2</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>72.8</v>
       </c>
       <c r="N27" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+        <v>9.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>57.1</v>
+      </c>
       <c r="R27" t="n">
-        <v>3.27</v>
+        <v>0.78</v>
       </c>
       <c r="S27" t="n">
-        <v>-29.2</v>
+        <v>-45.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.71</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／週斜率為正／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>— 不符</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>·····  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／現金／估值／品質／資金</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12/12</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>-0.37</v>
-      </c>
+          <t>0/12</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>-131.4</v>
+        <v>7.1</v>
       </c>
       <c r="K28" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>19.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>87.8</v>
+        <v>99.3</v>
       </c>
       <c r="N28" t="n">
-        <v>12.5</v>
+        <v>-2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.8</v>
+      </c>
       <c r="R28" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="S28" t="n">
-        <v>-59.2</v>
+        <v>-8.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.43</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
+          <t>— 不符</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>✔···✔  (成長現金估值品質資金)</t>
+          <t>·····  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>現金／估值／品質</t>
+          <t>成長／現金／估值／品質／資金</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>6/12</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-0.87</v>
+        <v>-2.15</v>
       </c>
       <c r="J29" t="n">
-        <v>-840.7</v>
+        <v>-2.4</v>
       </c>
       <c r="K29" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L29" t="n">
-        <v>76.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>98.7</v>
+        <v>78.7</v>
       </c>
       <c r="N29" t="n">
-        <v>35.3</v>
+        <v>1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>95.2</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>52.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>38.1</v>
+        <v>23.8</v>
       </c>
       <c r="R29" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>-43.6</v>
+        <v>-45.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>-1.52</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
+          <t>站上200日線／均線多頭／大盤多頭</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
+          <t>— 不符</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>····✔  (成長現金估值品質資金)</t>
+          <t>·····  (成長現金估值品質資金)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>成長／現金／估值／品質</t>
+          <t>成長／現金／估值／品質／資金</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2776,1069 +2810,47 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6/12</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>-1.84</v>
-      </c>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>-606.8</v>
+        <v>-9.5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>94.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="N30" t="n">
-        <v>8.9</v>
+        <v>-0.1</v>
       </c>
       <c r="O30" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23.8</v>
+      </c>
       <c r="R30" t="n">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>20.1</v>
+        <v>-56.2</v>
       </c>
       <c r="T30" t="n">
-        <v>3.11</v>
+        <v>-0.61</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>45</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>····✔  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>90</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>5/12</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-287.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>19</v>
-      </c>
-      <c r="L31" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>100</v>
-      </c>
-      <c r="N31" t="n">
-        <v>11</v>
-      </c>
-      <c r="O31" t="n">
-        <v>19</v>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="S31" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS上升／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>45</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>····✔  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>90</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>4/12</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-130.1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="L32" t="n">
-        <v>100</v>
-      </c>
-      <c r="M32" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="N32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O32" t="n">
-        <v>19</v>
-      </c>
-      <c r="P32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="S32" t="n">
-        <v>119.4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／價格創52週高／RS創52週高／RS上升／週斜率為正／週斜率加速／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>45</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>○ 偏多</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>✔✔···  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>40</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>12/12</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J33" t="n">
-        <v>378.2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="M33" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="N33" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="O33" t="n">
-        <v>100</v>
-      </c>
-      <c r="P33" t="n">
-        <v>-554.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>站上200日線／均線多頭／週斜率為正／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>42</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>🐢 穩定收租(牛皮績優·股息)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>·✔···  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>成長／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>60</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3/12</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J34" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="M34" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-58.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>站上200日線／均線多頭／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>42</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>— 不符</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>···✔·  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／資金</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>60</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>7/12</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K35" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="L35" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="M35" t="n">
-        <v>99</v>
-      </c>
-      <c r="N35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="P35" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S35" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>42</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>🔥 燒錢成長(成長吞現金)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>✔····  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>現金／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>60</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>12/12</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J36" t="n">
-        <v>-47.9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="N36" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="O36" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-59.4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>35</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>····✔  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>70</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>9/12</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M37" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O37" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="P37" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="S37" t="n">
-        <v>140.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／RS上升／週斜率為正／週斜率加速／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2332</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>35</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>⚠ 純資金(投機/慎防假突破)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>····✔  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>70</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>6/12</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>85</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="O38" t="n">
-        <v>19</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>-47.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／價格創52週高／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>30</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>— 不符</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>·····  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>60</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0/12</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K39" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="M39" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="N39" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="S39" t="n">
-        <v>-45.8</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>30</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>— 不符</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>·····  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>60</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0/12</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="O40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P40" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S40" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／均線多頭／週斜率為正／週斜率加速／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>30</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>— 不符</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>·····  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>60</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>8/12</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-65.5</v>
-      </c>
-      <c r="K41" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="L41" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O41" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="S41" t="n">
-        <v>-70.09999999999999</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>站上200日線／站上50日線／週斜率為正／週斜率加速／量能放大／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>15</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>— 不符</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>·····  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>30</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>8/12</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>19</v>
-      </c>
-      <c r="P42" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S42" t="n">
-        <v>-56.2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>站上200日線／均線多頭／大盤多頭</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2419</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>15</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>— 不符</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>·····  (成長現金估值品質資金)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>成長／現金／估值／品質／資金</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>30</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>6/12</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O43" t="n">
-        <v>19</v>
-      </c>
-      <c r="P43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>-45.3</v>
-      </c>
-      <c r="T43" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
         <is>
           <t>站上200日線／均線多頭／大盤多頭</t>
         </is>
@@ -3855,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5123,474 +4135,6 @@
       <c r="L30" t="n">
         <v>-554.8</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>784.3</v>
-      </c>
-      <c r="C31" t="n">
-        <v>856.1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G31" t="n">
-        <v>784.3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>97</v>
-      </c>
-      <c r="J31" t="n">
-        <v>100</v>
-      </c>
-      <c r="K31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1773.9</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1070.7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1773.9</v>
-      </c>
-      <c r="H32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I32" t="n">
-        <v>90</v>
-      </c>
-      <c r="J32" t="n">
-        <v>100</v>
-      </c>
-      <c r="K32" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>-287.9</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1134.4</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-287.9</v>
-      </c>
-      <c r="H33" t="n">
-        <v>19</v>
-      </c>
-      <c r="I33" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" t="n">
-        <v>11</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>821.7</v>
-      </c>
-      <c r="C34" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="G34" t="n">
-        <v>821.7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I34" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="J34" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="K34" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>-131.4</v>
-      </c>
-      <c r="C35" t="n">
-        <v>356.3</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-131.4</v>
-      </c>
-      <c r="H35" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="K35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>-403.8</v>
-      </c>
-      <c r="C36" t="n">
-        <v>467.6</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-403.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I36" t="n">
-        <v>100</v>
-      </c>
-      <c r="J36" t="n">
-        <v>100</v>
-      </c>
-      <c r="K36" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>-372.2</v>
-      </c>
-      <c r="C37" t="n">
-        <v>536.8</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-372.2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I37" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="K37" t="n">
-        <v>9</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-98.5</v>
-      </c>
-      <c r="C38" t="n">
-        <v>305.2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-98.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>19</v>
-      </c>
-      <c r="I38" t="n">
-        <v>100</v>
-      </c>
-      <c r="J38" t="n">
-        <v>100</v>
-      </c>
-      <c r="K38" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-453.5</v>
-      </c>
-      <c r="C39" t="n">
-        <v>279.7</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-453.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I39" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="J39" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="K39" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>798.1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G40" t="n">
-        <v>798.1</v>
-      </c>
-      <c r="H40" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="J40" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="K40" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-606.8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>330.4</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-606.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="I41" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>100</v>
-      </c>
-      <c r="K41" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-550.4</v>
-      </c>
-      <c r="C42" t="n">
-        <v>188.6</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-550.4</v>
-      </c>
-      <c r="H42" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I42" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="K42" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>-65.5</v>
-      </c>
-      <c r="C43" t="n">
-        <v>222.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-65.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="I43" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5603,7 +4147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6416,357 +4960,6 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
